--- a/data/trans_camb/IP12-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 6,73</t>
+          <t>-11,48; 6,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 14,86</t>
+          <t>-5,44; 14,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 0,75</t>
+          <t>-15,47; 0,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 9,91</t>
+          <t>-11,65; 9,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 13,0</t>
+          <t>-8,14; 13,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,68; -1,92</t>
+          <t>-18,07; -1,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 5,58</t>
+          <t>-8,22; 5,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 11,06</t>
+          <t>-3,63; 10,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,25; -1,96</t>
+          <t>-14,05; -2,41</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,59; 122,15</t>
+          <t>-71,79; 110,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 215,43</t>
+          <t>-42,19; 216,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,22; 33,73</t>
+          <t>-90,28; 21,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,35; 123,98</t>
+          <t>-65,07; 119,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 158,65</t>
+          <t>-45,54; 194,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-94,85; 17,07</t>
+          <t>-100,0; 19,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 64,21</t>
+          <t>-55,54; 66,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 129,39</t>
+          <t>-25,21; 118,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,0; -17,47</t>
+          <t>-85,64; -17,05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 9,27</t>
+          <t>-4,98; 8,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 5,96</t>
+          <t>-7,45; 6,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 4,1</t>
+          <t>-9,76; 4,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,98</t>
+          <t>1,3; 13,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 7,38</t>
+          <t>-2,98; 7,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,59</t>
+          <t>-4,03; 6,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 9,01</t>
+          <t>0,11; 9,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 5,45</t>
+          <t>-3,56; 4,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,79</t>
+          <t>-5,16; 3,29</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,19; 139,84</t>
+          <t>-39,08; 118,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,46; 90,86</t>
+          <t>-57,78; 102,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 56,83</t>
+          <t>-70,56; 56,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 461,25</t>
+          <t>5,43; 401,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 272,13</t>
+          <t>-44,45; 250,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,24; 206,14</t>
+          <t>-56,08; 199,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 162,84</t>
+          <t>-2,17; 164,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 105,09</t>
+          <t>-38,3; 76,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 60,79</t>
+          <t>-53,98; 55,09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 15,4</t>
+          <t>-0,39; 15,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 4,2</t>
+          <t>-6,84; 4,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 15,16</t>
+          <t>-0,91; 14,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 13,55</t>
+          <t>-0,33; 13,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 1,96</t>
+          <t>-7,16; 2,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 11,99</t>
+          <t>-2,09; 12,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 12,13</t>
+          <t>1,7; 12,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 1,37</t>
+          <t>-5,89; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,22</t>
+          <t>-0,09; 11,06</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 805,4</t>
+          <t>-19,94; 937,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 346,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 995,08</t>
+          <t>-32,02; 815,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 637,8</t>
+          <t>-20,79; 1039,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 220,59</t>
+          <t>-100,0; 220,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 743,49</t>
+          <t>-44,74; 688,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 450,53</t>
+          <t>14,68; 480,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-87,11; 74,72</t>
+          <t>-86,3; 92,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 409,87</t>
+          <t>-14,94; 411,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 10,8</t>
+          <t>-5,26; 10,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 12,25</t>
+          <t>-3,69; 12,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 4,79</t>
+          <t>-9,61; 5,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 4,33</t>
+          <t>-11,3; 5,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 10,84</t>
+          <t>-5,64; 10,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 9,78</t>
+          <t>-9,91; 10,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 5,58</t>
+          <t>-5,85; 5,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 9,09</t>
+          <t>-2,79; 8,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 4,56</t>
+          <t>-7,39; 4,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 202,06</t>
+          <t>-48,81; 192,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 244,56</t>
+          <t>-34,5; 237,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,59; 90,2</t>
+          <t>-79,93; 133,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 67,38</t>
+          <t>-76,75; 73,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,52; 181,65</t>
+          <t>-42,39; 166,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,53; 171,29</t>
+          <t>-73,65; 163,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 85,8</t>
+          <t>-47,26; 74,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 130,83</t>
+          <t>-24,51; 124,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,31; 67,39</t>
+          <t>-68,73; 62,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 28,4</t>
+          <t>5,59; 28,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 18,12</t>
+          <t>0,16; 17,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 16,16</t>
+          <t>-0,95; 16,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,4; 21,63</t>
+          <t>4,83; 21,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 7,81</t>
+          <t>-2,97; 7,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 12,89</t>
+          <t>-0,34; 12,96</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,51; 21,83</t>
+          <t>7,48; 21,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 10,28</t>
+          <t>0,42; 10,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,53</t>
+          <t>1,28; 11,74</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,93; —</t>
+          <t>38,87; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,88; —</t>
+          <t>-54,53; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,82; —</t>
+          <t>-57,87; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,24 +1677,24 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>105,49; 2949,16</t>
+          <t>105,58; 2403,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 1169,58</t>
+          <t>-16,86; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 1297,07</t>
+          <t>-0,95; 1725,15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 11,1</t>
+          <t>-5,61; 12,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -0,07</t>
+          <t>-12,88; 0,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 10,5</t>
+          <t>-5,65; 11,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 10,81</t>
+          <t>-3,29; 10,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 4,82</t>
+          <t>-7,45; 5,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,21; 22,34</t>
+          <t>3,92; 22,38</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 8,94</t>
+          <t>-2,75; 8,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 0,37</t>
+          <t>-8,14; 0,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,2; 14,55</t>
+          <t>2,16; 14,92</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 449,58</t>
+          <t>-65,51; 461,8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 339,14</t>
+          <t>-100,0; 202,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-62,69; 402,0</t>
+          <t>-63,34; 378,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 516,26</t>
+          <t>-55,27; 487,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 350,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40,88; 1293,35</t>
+          <t>37,95; 1329,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 280,05</t>
+          <t>-33,57; 255,12</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-93,21; 32,48</t>
+          <t>-100,0; 30,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>22,36; 442,93</t>
+          <t>23,65; 465,92</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,74</t>
+          <t>-5,13; 3,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 2,73</t>
+          <t>-5,69; 2,95</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 9,58</t>
+          <t>-1,01; 9,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,79</t>
+          <t>-2,66; 4,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,62</t>
+          <t>-2,85; 3,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,41; 11,05</t>
+          <t>1,68; 11,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,57</t>
+          <t>-2,48; 3,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,2</t>
+          <t>-3,05; 2,03</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,6; 9,07</t>
+          <t>1,37; 8,64</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 114,55</t>
+          <t>-64,64; 94,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-71,96; 91,11</t>
+          <t>-70,78; 112,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 290,27</t>
+          <t>-15,06; 266,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 346,96</t>
+          <t>-63,15; 376,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-68,71; 260,63</t>
+          <t>-71,2; 290,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,4; 829,97</t>
+          <t>15,58; 957,75</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 122,75</t>
+          <t>-46,52; 110,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-60,74; 72,06</t>
+          <t>-55,06; 64,77</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>19,15; 290,6</t>
+          <t>19,81; 305,48</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,78</t>
+          <t>-2,76; 3,94</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,72</t>
+          <t>0,85; 8,7</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,27</t>
+          <t>-3,46; 2,68</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 1,99</t>
+          <t>-7,79; 1,27</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 1,39</t>
+          <t>-8,12; 1,81</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 1,33</t>
+          <t>-8,11; 1,42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,79</t>
+          <t>-3,97; 1,38</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,72</t>
+          <t>-2,27; 3,51</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,9</t>
+          <t>-4,84; 1,01</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-55,29; 181,07</t>
+          <t>-60,35; 184,76</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>9,19; 398,61</t>
+          <t>4,32; 403,92</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-70,35; 108,32</t>
+          <t>-68,03; 156,3</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-66,94; 34,43</t>
+          <t>-67,99; 25,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-68,04; 24,97</t>
+          <t>-66,91; 36,83</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 23,7</t>
+          <t>-69,55; 30,08</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-48,95; 42,83</t>
+          <t>-52,28; 28,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 74,64</t>
+          <t>-29,79; 71,06</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-61,1; 23,02</t>
+          <t>-60,39; 23,1</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,46</t>
+          <t>-0,31; 4,41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,77</t>
+          <t>-0,9; 3,59</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,31</t>
+          <t>-1,53; 3,14</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,17</t>
+          <t>-0,51; 3,95</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,97</t>
+          <t>-2,04; 2,14</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,56</t>
+          <t>-1,06; 3,86</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,88</t>
+          <t>0,36; 3,67</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,3</t>
+          <t>-0,68; 2,37</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,66</t>
+          <t>-0,58; 2,63</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 80,85</t>
+          <t>-5,0; 81,05</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 69,18</t>
+          <t>-13,17; 66,76</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 59,9</t>
+          <t>-21,57; 57,45</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 71,89</t>
+          <t>-7,28; 69,01</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 34,06</t>
+          <t>-26,39; 38,65</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 62,95</t>
+          <t>-13,37; 67,73</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,62; 67,37</t>
+          <t>5,84; 64,64</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 41,49</t>
+          <t>-9,77; 42,04</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 47,48</t>
+          <t>-8,73; 44,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 6,14</t>
+          <t>-12,46; 5,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 14,55</t>
+          <t>-5,58; 15,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 0,09</t>
+          <t>-14,71; 1,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 9,22</t>
+          <t>-10,35; 10,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 13,05</t>
+          <t>-8,47; 12,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -1,07</t>
+          <t>-17,74; -0,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 5,34</t>
+          <t>-8,42; 6,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 10,79</t>
+          <t>-3,42; 11,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -2,41</t>
+          <t>-14,08; -2,15</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,79; 110,52</t>
+          <t>-77,35; 118,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 216,77</t>
+          <t>-38,74; 252,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,28; 21,59</t>
+          <t>-89,54; 50,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-65,07; 119,5</t>
+          <t>-57,55; 141,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 194,92</t>
+          <t>-49,3; 155,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 19,93</t>
+          <t>-100,0; 6,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 66,61</t>
+          <t>-52,98; 68,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 118,41</t>
+          <t>-24,14; 134,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,64; -17,05</t>
+          <t>-85,61; -18,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 8,47</t>
+          <t>-5,47; 8,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 6,38</t>
+          <t>-6,93; 5,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 4,03</t>
+          <t>-10,01; 3,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 13,18</t>
+          <t>1,31; 14,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 7,24</t>
+          <t>-2,82; 7,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 6,51</t>
+          <t>-3,75; 5,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 9,6</t>
+          <t>-0,14; 8,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 4,63</t>
+          <t>-3,49; 4,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 3,29</t>
+          <t>-5,63; 3,2</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 118,71</t>
+          <t>-45,16; 112,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,78; 102,98</t>
+          <t>-52,49; 81,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,56; 56,73</t>
+          <t>-71,75; 49,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 401,27</t>
+          <t>3,3; 492,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,45; 250,51</t>
+          <t>-40,03; 292,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,08; 199,62</t>
+          <t>-56,59; 214,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 164,76</t>
+          <t>-3,61; 153,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,3; 76,54</t>
+          <t>-36,28; 89,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-53,98; 55,09</t>
+          <t>-55,73; 55,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 15,04</t>
+          <t>-0,22; 15,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,17</t>
+          <t>-6,82; 4,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 14,31</t>
+          <t>-1,3; 14,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 13,88</t>
+          <t>-1,24; 13,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 2,11</t>
+          <t>-7,19; 2,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 12,03</t>
+          <t>-2,36; 12,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 12,07</t>
+          <t>1,53; 12,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,61</t>
+          <t>-5,33; 1,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 11,06</t>
+          <t>0,44; 10,75</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 937,12</t>
+          <t>-11,94; 1170,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 815,25</t>
+          <t>-35,89; 875,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 1039,75</t>
+          <t>-33,61; 609,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 220,54</t>
+          <t>-100,0; 170,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 688,25</t>
+          <t>-47,06; 605,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,68; 480,89</t>
+          <t>8,5; 431,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-86,3; 92,46</t>
+          <t>-82,3; 91,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 411,28</t>
+          <t>-2,31; 387,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 10,35</t>
+          <t>-5,16; 10,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 12,69</t>
+          <t>-3,45; 13,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 5,01</t>
+          <t>-10,27; 4,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 5,11</t>
+          <t>-10,16; 5,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 10,05</t>
+          <t>-6,38; 10,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 10,15</t>
+          <t>-10,02; 8,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 5,35</t>
+          <t>-5,53; 4,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 8,96</t>
+          <t>-2,2; 9,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 4,45</t>
+          <t>-7,93; 4,48</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 192,07</t>
+          <t>-41,9; 209,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 237,25</t>
+          <t>-34,46; 264,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,93; 133,05</t>
+          <t>-82,62; 88,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-76,75; 73,57</t>
+          <t>-72,72; 85,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 166,99</t>
+          <t>-44,54; 147,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 163,06</t>
+          <t>-81,46; 133,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 74,74</t>
+          <t>-46,54; 68,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 124,4</t>
+          <t>-23,03; 130,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,73; 62,01</t>
+          <t>-65,64; 66,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,59; 28,23</t>
+          <t>5,97; 28,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 17,03</t>
+          <t>-0,79; 16,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 16,89</t>
+          <t>-0,85; 15,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,83; 21,65</t>
+          <t>4,48; 21,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 7,96</t>
+          <t>-2,99; 7,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 12,96</t>
+          <t>-0,35; 13,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,48; 21,7</t>
+          <t>7,13; 21,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 10,37</t>
+          <t>-0,08; 9,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,74</t>
+          <t>1,06; 11,87</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>38,87; —</t>
+          <t>32,61; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-54,53; —</t>
+          <t>-65,41; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,87; —</t>
+          <t>-54,21; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>105,58; 2403,57</t>
+          <t>95,5; 2496,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,86; —</t>
+          <t>-36,42; 1196,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1725,15</t>
+          <t>-12,62; 1404,79</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 12,32</t>
+          <t>-5,36; 11,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 0,14</t>
+          <t>-12,13; 0,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 11,04</t>
+          <t>-5,06; 12,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 10,81</t>
+          <t>-3,67; 10,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 5,17</t>
+          <t>-8,0; 3,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,92; 22,38</t>
+          <t>3,57; 22,53</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 8,4</t>
+          <t>-2,31; 8,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 0,32</t>
+          <t>-7,96; 0,41</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,16; 14,92</t>
+          <t>2,34; 14,9</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-65,51; 461,8</t>
+          <t>-57,19; 485,58</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 202,17</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,34; 378,24</t>
+          <t>-61,84; 706,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-55,27; 487,64</t>
+          <t>-63,88; 547,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 350,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,95; 1329,72</t>
+          <t>27,22; 1241,31</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 255,12</t>
+          <t>-31,3; 257,87</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,75</t>
+          <t>-96,56; 33,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>23,65; 465,92</t>
+          <t>17,9; 403,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,3</t>
+          <t>-5,64; 3,29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 2,95</t>
+          <t>-6,63; 2,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 9,32</t>
+          <t>-1,18; 9,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 4,76</t>
+          <t>-2,89; 5,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 3,75</t>
+          <t>-3,02; 3,94</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,68; 11,47</t>
+          <t>1,55; 11,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,38</t>
+          <t>-2,58; 3,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,03</t>
+          <t>-3,49; 2,37</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,37; 8,64</t>
+          <t>1,39; 8,72</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 94,85</t>
+          <t>-68,32; 102,93</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-70,78; 112,63</t>
+          <t>-75,43; 72,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 266,89</t>
+          <t>-19,86; 265,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-63,15; 376,52</t>
+          <t>-64,6; 293,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 290,93</t>
+          <t>-68,15; 329,25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,58; 957,75</t>
+          <t>22,25; 790,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-46,52; 110,64</t>
+          <t>-46,73; 115,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-55,06; 64,77</t>
+          <t>-57,21; 89,86</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>19,81; 305,48</t>
+          <t>16,66; 296,12</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,94</t>
+          <t>-2,66; 3,96</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,7</t>
+          <t>0,78; 8,82</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 2,68</t>
+          <t>-3,65; 2,73</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 1,27</t>
+          <t>-7,76; 1,72</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 1,81</t>
+          <t>-7,47; 1,99</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 1,42</t>
+          <t>-8,08; 1,53</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,38</t>
+          <t>-4,04; 1,69</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,51</t>
+          <t>-1,99; 4,03</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,01</t>
+          <t>-4,73; 0,89</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-60,35; 184,76</t>
+          <t>-51,36; 214,73</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4,32; 403,92</t>
+          <t>6,63; 397,1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-68,03; 156,3</t>
+          <t>-70,1; 153,84</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-67,99; 25,83</t>
+          <t>-66,13; 32,28</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-66,91; 36,83</t>
+          <t>-63,9; 31,47</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-69,55; 30,08</t>
+          <t>-69,16; 28,95</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 28,99</t>
+          <t>-51,29; 38,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,79; 71,06</t>
+          <t>-25,4; 86,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 23,1</t>
+          <t>-61,26; 23,32</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,41</t>
+          <t>-0,17; 4,56</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,59</t>
+          <t>-0,62; 3,81</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,14</t>
+          <t>-1,82; 2,67</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,95</t>
+          <t>-0,38; 4,06</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,14</t>
+          <t>-2,21; 2,03</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,86</t>
+          <t>-0,89; 3,65</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,67</t>
+          <t>0,44; 3,63</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,37</t>
+          <t>-0,8; 2,22</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,63</t>
+          <t>-0,74; 2,56</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 81,05</t>
+          <t>-2,67; 84,31</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 66,76</t>
+          <t>-10,06; 71,9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 57,45</t>
+          <t>-23,69; 48,84</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 69,01</t>
+          <t>-5,66; 72,04</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 38,65</t>
+          <t>-28,86; 35,74</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 67,73</t>
+          <t>-11,73; 68,18</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>5,84; 64,64</t>
+          <t>6,13; 61,11</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 42,04</t>
+          <t>-10,75; 38,64</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 44,17</t>
+          <t>-10,59; 43,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,62</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-8,94</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,08</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,1</t>
+          <t>-5,52</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,78</t>
+          <t>-7,35</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 5,94</t>
+          <t>-10,68; 9,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 15,53</t>
+          <t>-8,26; 13,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 1,37</t>
+          <t>-19,49; -1,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 10,53</t>
+          <t>-12,17; 6,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 12,78</t>
+          <t>-5,19; 14,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,74; -0,63</t>
+          <t>-14,14; 1,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 6,08</t>
+          <t>-8,42; 5,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 11,54</t>
+          <t>-3,58; 11,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -2,15</t>
+          <t>-14,07; -1,52</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-3,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19,97%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-68,25%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-20,97%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>46,66%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-57,74%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,15%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,97%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-69,42%</t>
+          <t>-50,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-64,44%</t>
+          <t>-60,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-77,35; 118,2</t>
+          <t>-61,35; 123,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 252,74</t>
+          <t>-44,94; 158,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-89,54; 50,47</t>
+          <t>-94,71; 19,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 141,76</t>
+          <t>-76,59; 122,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 155,78</t>
+          <t>-36,88; 215,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6,38</t>
+          <t>-87,52; 50,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 68,68</t>
+          <t>-55,31; 64,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 134,65</t>
+          <t>-22,9; 129,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,61; -18,33</t>
+          <t>-85,04; -10,86</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,91</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,56</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,65</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,16</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>0,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 8,34</t>
+          <t>1,51; 13,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 5,86</t>
+          <t>-3,33; 7,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 3,77</t>
+          <t>-4,62; 5,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,63</t>
+          <t>-5,08; 9,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 7,63</t>
+          <t>-7,76; 5,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,71</t>
+          <t>-7,53; 6,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 8,94</t>
+          <t>-0,03; 9,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 4,93</t>
+          <t>-3,43; 5,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,2</t>
+          <t>-4,13; 4,67</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>133,78%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,53%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>14,2%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-6,96%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-26,06%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>133,78%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35,68%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>-4,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-11,33%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,16; 112,51</t>
+          <t>3,49; 461,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 81,76</t>
+          <t>-44,93; 272,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,75; 49,91</t>
+          <t>-61,94; 197,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 492,11</t>
+          <t>-38,19; 139,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 292,82</t>
+          <t>-56,46; 90,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,59; 214,93</t>
+          <t>-56,39; 87,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 153,0</t>
+          <t>-1,19; 162,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 89,48</t>
+          <t>-35,9; 105,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 55,02</t>
+          <t>-44,26; 84,94</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,52</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,04</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,26</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,55</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,76</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,52</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>5,07</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 15,91</t>
+          <t>-0,64; 13,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 4,42</t>
+          <t>-7,22; 1,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 14,36</t>
+          <t>-2,53; 11,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 13,39</t>
+          <t>-0,37; 15,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 2,08</t>
+          <t>-6,81; 4,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 12,19</t>
+          <t>-0,94; 14,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 12,21</t>
+          <t>1,34; 12,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1,8</t>
+          <t>-5,85; 1,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 10,75</t>
+          <t>-0,25; 9,89</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>129,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-56,55%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90,64%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>163,2%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-28,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>146,51%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>129,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-56,55%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>137,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>117,59%</t>
+          <t>113,42%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 1170,83</t>
+          <t>-24,6; 637,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 220,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 875,01</t>
+          <t>-48,2; 709,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 609,7</t>
+          <t>-21,95; 805,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 170,88</t>
+          <t>-100,0; 346,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 605,35</t>
+          <t>-27,34; 942,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,5; 431,34</t>
+          <t>6,5; 450,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,3; 91,84</t>
+          <t>-87,11; 74,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 387,67</t>
+          <t>-11,19; 400,66</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,37</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,61</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,57</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-1,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 10,66</t>
+          <t>-10,76; 4,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 13,57</t>
+          <t>-5,64; 10,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 4,56</t>
+          <t>-9,68; 11,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 5,29</t>
+          <t>-4,79; 10,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 10,1</t>
+          <t>-3,73; 12,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 8,87</t>
+          <t>-8,99; 5,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,82</t>
+          <t>-5,64; 5,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 9,18</t>
+          <t>-3,15; 9,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 4,48</t>
+          <t>-7,27; 5,61</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-25,23%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-10,01%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>27,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>48,39%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-32,44%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-25,23%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>22,9%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,19%</t>
+          <t>-27,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-22,39%</t>
+          <t>-17,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 209,53</t>
+          <t>-74,0; 67,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 264,02</t>
+          <t>-42,52; 181,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,62; 88,14</t>
+          <t>-79,12; 193,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-72,72; 85,26</t>
+          <t>-45,4; 202,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 147,1</t>
+          <t>-34,51; 244,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,46; 133,04</t>
+          <t>-79,49; 115,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-46,54; 68,13</t>
+          <t>-47,73; 85,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 130,03</t>
+          <t>-27,63; 130,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,64; 66,21</t>
+          <t>-64,86; 82,91</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12,14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,37</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,61</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>15,93</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>7,2</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7,0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12,14</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,37</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,1</t>
+          <t>6,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,97; 28,36</t>
+          <t>4,4; 21,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 16,36</t>
+          <t>-2,56; 7,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 15,7</t>
+          <t>-0,28; 13,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,48; 21,62</t>
+          <t>6,23; 28,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 7,76</t>
+          <t>-0,34; 18,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 13,4</t>
+          <t>-0,54; 15,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,13; 21,62</t>
+          <t>7,51; 21,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,44</t>
+          <t>0,02; 10,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 11,87</t>
+          <t>1,15; 11,66</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>818,34%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>159,48%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>378,42%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>500,22%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>226,18%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>219,77%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>818,34%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>159,48%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>364,43%</t>
+          <t>220,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>264,52%</t>
+          <t>271,82%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>32,61; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-65,41; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,21; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,93; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-55,88; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,26; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,5; 2496,17</t>
+          <t>105,49; 2949,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-36,42; 1196,7</t>
+          <t>-28,78; 1169,58</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 1404,79</t>
+          <t>-6,36; 1305,7</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-2,1</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>12,57</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,8</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-5,19</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3,2</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-2,1</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,71</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>7,65</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 11,51</t>
+          <t>-3,88; 10,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 0,15</t>
+          <t>-7,85; 4,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 12,06</t>
+          <t>4,05; 22,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 10,97</t>
+          <t>-5,86; 11,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 3,87</t>
+          <t>-11,91; -0,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,57; 22,53</t>
+          <t>-5,43; 10,29</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 8,57</t>
+          <t>-2,37; 8,94</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 0,41</t>
+          <t>-8,06; 0,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,34; 14,9</t>
+          <t>1,91; 14,15</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>61,96%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-40,74%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>243,6%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>42,79%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-79,44%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>61,96%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-40,74%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>246,36%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>137,83%</t>
+          <t>131,35%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 485,58</t>
+          <t>-62,73; 516,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-61,84; 706,84</t>
+          <t>41,94; 1290,07</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 547,48</t>
+          <t>-60,95; 449,58</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 339,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,22; 1241,31</t>
+          <t>-63,33; 399,47</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 257,87</t>
+          <t>-35,18; 280,05</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-96,56; 33,92</t>
+          <t>-93,21; 32,48</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17,9; 403,1</t>
+          <t>18,97; 432,67</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6,86</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-0,73</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,55</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,94</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,94</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>5,51</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 3,29</t>
+          <t>-2,72; 4,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 2,39</t>
+          <t>-2,64; 3,62</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 9,46</t>
+          <t>2,08; 12,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 5,04</t>
+          <t>-5,01; 3,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 3,94</t>
+          <t>-6,1; 2,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,55; 11,32</t>
+          <t>-0,72; 9,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,35</t>
+          <t>-2,59; 3,57</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,37</t>
+          <t>-3,65; 2,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,72</t>
+          <t>1,98; 9,73</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>39,03%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>230,06%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-12,35%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-26,41%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>66,91%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>39,03%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>12,87%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>199,44%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>112,17%</t>
+          <t>125,48%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-68,32; 102,93</t>
+          <t>-64,01; 346,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-75,43; 72,73</t>
+          <t>-68,71; 260,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 265,05</t>
+          <t>26,96; 919,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 293,22</t>
+          <t>-65,92; 114,55</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-68,15; 329,25</t>
+          <t>-71,96; 91,11</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,25; 790,52</t>
+          <t>-12,0; 299,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 115,33</t>
+          <t>-47,87; 122,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-57,21; 89,86</t>
+          <t>-60,74; 72,06</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>16,66; 296,12</t>
+          <t>29,49; 314,26</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-2,84</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-2,87</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-3,41</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>4,62</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-2,87</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-3,3</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-2,27</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 3,96</t>
+          <t>-7,53; 1,99</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,78; 8,82</t>
+          <t>-7,86; 1,39</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,73</t>
+          <t>-8,31; 1,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 1,72</t>
+          <t>-2,82; 3,78</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 1,99</t>
+          <t>0,84; 8,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 1,53</t>
+          <t>-4,38; 1,28</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,69</t>
+          <t>-3,91; 1,79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,03</t>
+          <t>-2,35; 3,72</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,89</t>
+          <t>-4,92; 0,49</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-32,0%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-32,29%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-38,38%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>13,68%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>125,63%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-17,51%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-32,0%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-32,29%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-37,17%</t>
+          <t>-32,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-30,2%</t>
+          <t>-35,8%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-51,36; 214,73</t>
+          <t>-66,94; 34,43</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>6,63; 397,1</t>
+          <t>-68,04; 24,97</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-70,1; 153,84</t>
+          <t>-72,81; 25,11</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-66,13; 32,28</t>
+          <t>-55,29; 181,07</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-63,9; 31,47</t>
+          <t>9,19; 398,61</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-69,16; 28,95</t>
+          <t>-77,59; 67,49</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-51,29; 38,48</t>
+          <t>-48,95; 42,83</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-25,4; 86,39</t>
+          <t>-29,81; 74,64</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-61,26; 23,32</t>
+          <t>-64,95; 12,89</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>2,17</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,56</t>
+          <t>-0,27; 4,17</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,81</t>
+          <t>-2,16; 1,97</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,67</t>
+          <t>-1,17; 3,76</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,06</t>
+          <t>-0,06; 4,46</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,03</t>
+          <t>-0,88; 3,77</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,65</t>
+          <t>-1,16; 3,56</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,63</t>
+          <t>0,61; 3,88</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,22</t>
+          <t>-0,95; 2,3</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,56</t>
+          <t>-0,33; 3,06</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>28,63%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-0,74%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>20,55%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>33,72%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>22,9%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>28,63%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-0,74%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 84,31</t>
+          <t>-4,72; 71,89</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 71,9</t>
+          <t>-28,71; 34,06</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 48,84</t>
+          <t>-15,48; 66,4</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 72,04</t>
+          <t>-1,3; 80,85</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 35,74</t>
+          <t>-11,39; 69,18</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 68,18</t>
+          <t>-15,97; 69,01</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,13; 61,11</t>
+          <t>7,62; 67,37</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 38,64</t>
+          <t>-13,13; 41,49</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 43,58</t>
+          <t>-5,75; 52,29</t>
         </is>
       </c>
     </row>
